--- a/venv/foody/output/Da Nang import.xlsx
+++ b/venv/foody/output/Da Nang import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin Data\PycharmProjects\pythonProject1\github\Code_python\venv\foody\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150DBC12-1B0D-4127-B0DC-EDA18A8CBCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611BF546-3E6E-4372-9691-BFACABA66F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
